--- a/reports/pdf_change_20260929.xlsx
+++ b/reports/pdf_change_20260929.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 5/7  ·  대기: RISE, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,865억   ·   현금 17억(0.4%)      당일 2026-09-29  vs  전영업일 2026-09-28      매수 4종목  /  매도 1종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,865억      당일 2026-09-29  vs  전영업일 2026-09-28      매수 4종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -791,7 +791,7 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,286억   ·   현금 38억(1.2%)      당일 2026-09-29  vs  전영업일 2026-09-28      매수 3종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,286억      당일 2026-09-29  vs  전영업일 2026-09-28      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -996,7 +996,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,643억   ·   현금 42억(1.6%)      당일 2026-09-29  vs  전영업일 2026-09-28      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,643억      당일 2026-09-29  vs  전영업일 2026-09-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1020,7 +1020,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,001억   ·   현금 34억(1.7%)      당일 2026-09-29  vs  전영업일 2026-09-28      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,001억      당일 2026-09-29  vs  전영업일 2026-09-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1044,7 +1044,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 300억   ·   현금 1억(0.4%)      당일 2026-09-29  vs  전영업일 2026-09-28      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 300억      당일 2026-09-29  vs  전영업일 2026-09-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1066,41 +1066,48 @@
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="20" t="n"/>
-      <c r="H27" s="20" t="n"/>
-      <c r="I27" s="20" t="n"/>
-      <c r="J27" s="20" t="n"/>
-      <c r="K27" s="20" t="n"/>
-    </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 8억(1.6%)      당일 2026-09-29  vs  전영업일 2026-09-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="20" t="n"/>
-      <c r="F29" s="20" t="n"/>
-      <c r="G29" s="20" t="n"/>
-      <c r="H29" s="20" t="n"/>
-      <c r="I29" s="20" t="n"/>
-      <c r="J29" s="20" t="n"/>
-      <c r="K29" s="20" t="n"/>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+      <c r="F30" s="20" t="n"/>
+      <c r="G30" s="20" t="n"/>
+      <c r="H30" s="20" t="n"/>
+      <c r="I30" s="20" t="n"/>
+      <c r="J30" s="20" t="n"/>
+      <c r="K30" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
@@ -1109,12 +1116,13 @@
     <mergeCell ref="G12:K12"/>
     <mergeCell ref="A21:K21"/>
     <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A30:K30"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A28:K28"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="G4:K4"/>
   </mergeCells>

--- a/reports/pdf_change_20260929.xlsx
+++ b/reports/pdf_change_20260929.xlsx
@@ -1068,7 +1068,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 8억(1.6%)      당일 2026-09-29  vs  전영업일 2026-09-28      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억      당일 2026-09-29  vs  전영업일 2026-09-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
